--- a/Stock_OneClick/stock_input_template.xlsx
+++ b/Stock_OneClick/stock_input_template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1_Input" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2_Classified" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sheet1_Input" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet2_Classified" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/Stock_OneClick/stock_input_template.xlsx
+++ b/Stock_OneClick/stock_input_template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1_Input" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet2_Classified" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1_Input" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2_Classified" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/Stock_OneClick/stock_input_template.xlsx
+++ b/Stock_OneClick/stock_input_template.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1068"/>
+  <dimension ref="A1:A1085"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7902,6 +7902,125 @@
       <c r="A1068" t="inlineStr">
         <is>
           <t>GLXY</t>
+        </is>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" t="inlineStr">
+        <is>
+          <t>GBTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" t="inlineStr">
+        <is>
+          <t>IBIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" t="inlineStr">
+        <is>
+          <t>FBTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" t="inlineStr">
+        <is>
+          <t>ARKB</t>
+        </is>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" t="inlineStr">
+        <is>
+          <t>BITB</t>
+        </is>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" t="inlineStr">
+        <is>
+          <t>BRRR</t>
+        </is>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" t="inlineStr">
+        <is>
+          <t>HODL</t>
+        </is>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" t="inlineStr">
+        <is>
+          <t>EZBC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" t="inlineStr">
+        <is>
+          <t>BTCO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" t="inlineStr">
+        <is>
+          <t>BITO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" t="inlineStr">
+        <is>
+          <t>BITX</t>
+        </is>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" t="inlineStr">
+        <is>
+          <t>MARA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" t="inlineStr">
+        <is>
+          <t>RIOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" t="inlineStr">
+        <is>
+          <t>CLSK</t>
+        </is>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" t="inlineStr">
+        <is>
+          <t>CORZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" t="inlineStr">
+        <is>
+          <t>CIFR</t>
+        </is>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" t="inlineStr">
+        <is>
+          <t>BTBT</t>
         </is>
       </c>
     </row>
@@ -7916,7 +8035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1068"/>
+  <dimension ref="A1:I1085"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12859,7 +12978,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>16 金融股</t>
+          <t>44 比特币概念</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -12945,7 +13064,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>16 金融股</t>
+          <t>44 比特币概念</t>
         </is>
       </c>
       <c r="H128" t="inlineStr"/>
@@ -14096,7 +14215,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>21 数据中心</t>
+          <t>44 比特币概念</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -26668,12 +26787,12 @@
       </c>
       <c r="G479" t="inlineStr">
         <is>
-          <t>29 软件 / 云</t>
+          <t>44 比特币概念</t>
         </is>
       </c>
       <c r="H479" t="inlineStr"/>
       <c r="I479" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="480">
@@ -29944,12 +30063,12 @@
       </c>
       <c r="G563" t="inlineStr">
         <is>
-          <t>29 软件 / 云</t>
+          <t>44 比特币概念</t>
         </is>
       </c>
       <c r="H563" t="inlineStr"/>
       <c r="I563" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="564">
@@ -39686,12 +39805,12 @@
       </c>
       <c r="G813" t="inlineStr">
         <is>
-          <t>23 金融科技 / 支付</t>
+          <t>44 比特币概念</t>
         </is>
       </c>
       <c r="H813" t="inlineStr"/>
       <c r="I813" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="814">
@@ -45653,12 +45772,12 @@
       </c>
       <c r="G966" t="inlineStr">
         <is>
-          <t>23 金融科技 / 支付</t>
+          <t>44 比特币概念</t>
         </is>
       </c>
       <c r="H966" t="inlineStr"/>
       <c r="I966" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="967">
@@ -46745,12 +46864,12 @@
       </c>
       <c r="G994" t="inlineStr">
         <is>
-          <t>29 软件 / 云</t>
+          <t>44 比特币概念</t>
         </is>
       </c>
       <c r="H994" t="inlineStr"/>
       <c r="I994" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="995">
@@ -49631,12 +49750,655 @@
       </c>
       <c r="G1068" t="inlineStr">
         <is>
-          <t>25 银行 / 金融</t>
+          <t>44 比特币概念</t>
         </is>
       </c>
       <c r="H1068" t="inlineStr"/>
       <c r="I1068" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" t="inlineStr">
+        <is>
+          <t>GBTC</t>
+        </is>
+      </c>
+      <c r="B1069" t="inlineStr">
+        <is>
+          <t>Grayscale Bitcoin Trust ETF</t>
+        </is>
+      </c>
+      <c r="C1069" t="inlineStr">
+        <is>
+          <t>PCX</t>
+        </is>
+      </c>
+      <c r="D1069" t="inlineStr"/>
+      <c r="E1069" t="inlineStr"/>
+      <c r="F1069" t="n">
+        <v>8394089984</v>
+      </c>
+      <c r="G1069" t="inlineStr">
+        <is>
+          <t>44 比特币概念</t>
+        </is>
+      </c>
+      <c r="H1069" t="inlineStr">
+        <is>
+          <t>added 2026-08-24: BTC-related sector grouping</t>
+        </is>
+      </c>
+      <c r="I1069" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" t="inlineStr">
+        <is>
+          <t>IBIT</t>
+        </is>
+      </c>
+      <c r="B1070" t="inlineStr">
+        <is>
+          <t>iShares Bitcoin Trust ETF</t>
+        </is>
+      </c>
+      <c r="C1070" t="inlineStr">
+        <is>
+          <t>NGM</t>
+        </is>
+      </c>
+      <c r="D1070" t="inlineStr"/>
+      <c r="E1070" t="inlineStr"/>
+      <c r="F1070" t="n">
+        <v>46523912192</v>
+      </c>
+      <c r="G1070" t="inlineStr">
+        <is>
+          <t>44 比特币概念</t>
+        </is>
+      </c>
+      <c r="H1070" t="inlineStr">
+        <is>
+          <t>added 2026-08-24: BTC-related sector grouping</t>
+        </is>
+      </c>
+      <c r="I1070" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" t="inlineStr">
+        <is>
+          <t>FBTC</t>
+        </is>
+      </c>
+      <c r="B1071" t="inlineStr">
+        <is>
+          <t>Fidelity Wise Origin Bitcoin Fund</t>
+        </is>
+      </c>
+      <c r="C1071" t="inlineStr">
+        <is>
+          <t>BTS</t>
+        </is>
+      </c>
+      <c r="D1071" t="inlineStr"/>
+      <c r="E1071" t="inlineStr"/>
+      <c r="F1071" t="n">
+        <v>10813950976</v>
+      </c>
+      <c r="G1071" t="inlineStr">
+        <is>
+          <t>44 比特币概念</t>
+        </is>
+      </c>
+      <c r="H1071" t="inlineStr">
+        <is>
+          <t>added 2026-08-24: BTC-related sector grouping</t>
+        </is>
+      </c>
+      <c r="I1071" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" t="inlineStr">
+        <is>
+          <t>ARKB</t>
+        </is>
+      </c>
+      <c r="B1072" t="inlineStr">
+        <is>
+          <t>ARK 21Shares Bitcoin ETF</t>
+        </is>
+      </c>
+      <c r="C1072" t="inlineStr">
+        <is>
+          <t>BTS</t>
+        </is>
+      </c>
+      <c r="D1072" t="inlineStr"/>
+      <c r="E1072" t="inlineStr"/>
+      <c r="F1072" t="n">
+        <v>2128186368</v>
+      </c>
+      <c r="G1072" t="inlineStr">
+        <is>
+          <t>44 比特币概念</t>
+        </is>
+      </c>
+      <c r="H1072" t="inlineStr">
+        <is>
+          <t>added 2026-08-24: BTC-related sector grouping</t>
+        </is>
+      </c>
+      <c r="I1072" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" t="inlineStr">
+        <is>
+          <t>BITB</t>
+        </is>
+      </c>
+      <c r="B1073" t="inlineStr">
+        <is>
+          <t>Bitwise Bitcoin ETF</t>
+        </is>
+      </c>
+      <c r="C1073" t="inlineStr">
+        <is>
+          <t>PCX</t>
+        </is>
+      </c>
+      <c r="D1073" t="inlineStr"/>
+      <c r="E1073" t="inlineStr"/>
+      <c r="F1073" t="n">
+        <v>2329154304</v>
+      </c>
+      <c r="G1073" t="inlineStr">
+        <is>
+          <t>44 比特币概念</t>
+        </is>
+      </c>
+      <c r="H1073" t="inlineStr">
+        <is>
+          <t>added 2026-08-24: BTC-related sector grouping</t>
+        </is>
+      </c>
+      <c r="I1073" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" t="inlineStr">
+        <is>
+          <t>BRRR</t>
+        </is>
+      </c>
+      <c r="B1074" t="inlineStr">
+        <is>
+          <t>CoinShares Bitcoin ETF</t>
+        </is>
+      </c>
+      <c r="C1074" t="inlineStr">
+        <is>
+          <t>NGM</t>
+        </is>
+      </c>
+      <c r="D1074" t="inlineStr"/>
+      <c r="E1074" t="inlineStr"/>
+      <c r="F1074" t="n">
+        <v>370854848</v>
+      </c>
+      <c r="G1074" t="inlineStr">
+        <is>
+          <t>44 比特币概念</t>
+        </is>
+      </c>
+      <c r="H1074" t="inlineStr">
+        <is>
+          <t>added 2026-08-24: BTC-related sector grouping</t>
+        </is>
+      </c>
+      <c r="I1074" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" t="inlineStr">
+        <is>
+          <t>HODL</t>
+        </is>
+      </c>
+      <c r="B1075" t="inlineStr">
+        <is>
+          <t>VanEck Bitcoin ETF</t>
+        </is>
+      </c>
+      <c r="C1075" t="inlineStr">
+        <is>
+          <t>BTS</t>
+        </is>
+      </c>
+      <c r="D1075" t="inlineStr"/>
+      <c r="E1075" t="inlineStr"/>
+      <c r="F1075" t="n">
+        <v>1048333632</v>
+      </c>
+      <c r="G1075" t="inlineStr">
+        <is>
+          <t>44 比特币概念</t>
+        </is>
+      </c>
+      <c r="H1075" t="inlineStr">
+        <is>
+          <t>added 2026-08-24: BTC-related sector grouping</t>
+        </is>
+      </c>
+      <c r="I1075" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" t="inlineStr">
+        <is>
+          <t>EZBC</t>
+        </is>
+      </c>
+      <c r="B1076" t="inlineStr">
+        <is>
+          <t>Franklin Bitcoin ETF</t>
+        </is>
+      </c>
+      <c r="C1076" t="inlineStr">
+        <is>
+          <t>BTS</t>
+        </is>
+      </c>
+      <c r="D1076" t="inlineStr"/>
+      <c r="E1076" t="inlineStr"/>
+      <c r="F1076" t="n">
+        <v>354688768</v>
+      </c>
+      <c r="G1076" t="inlineStr">
+        <is>
+          <t>44 比特币概念</t>
+        </is>
+      </c>
+      <c r="H1076" t="inlineStr">
+        <is>
+          <t>added 2026-08-24: BTC-related sector grouping</t>
+        </is>
+      </c>
+      <c r="I1076" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" t="inlineStr">
+        <is>
+          <t>BTCO</t>
+        </is>
+      </c>
+      <c r="B1077" t="inlineStr">
+        <is>
+          <t>Invesco Galaxy Bitcoin ETF</t>
+        </is>
+      </c>
+      <c r="C1077" t="inlineStr">
+        <is>
+          <t>BTS</t>
+        </is>
+      </c>
+      <c r="D1077" t="inlineStr"/>
+      <c r="E1077" t="inlineStr"/>
+      <c r="F1077" t="n">
+        <v>341665024</v>
+      </c>
+      <c r="G1077" t="inlineStr">
+        <is>
+          <t>44 比特币概念</t>
+        </is>
+      </c>
+      <c r="H1077" t="inlineStr">
+        <is>
+          <t>added 2026-08-24: BTC-related sector grouping</t>
+        </is>
+      </c>
+      <c r="I1077" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" t="inlineStr">
+        <is>
+          <t>BITO</t>
+        </is>
+      </c>
+      <c r="B1078" t="inlineStr">
+        <is>
+          <t>ProShares Bitcoin ETF</t>
+        </is>
+      </c>
+      <c r="C1078" t="inlineStr">
+        <is>
+          <t>PCX</t>
+        </is>
+      </c>
+      <c r="D1078" t="inlineStr"/>
+      <c r="E1078" t="inlineStr"/>
+      <c r="F1078" t="n">
+        <v>1405760896</v>
+      </c>
+      <c r="G1078" t="inlineStr">
+        <is>
+          <t>44 比特币概念</t>
+        </is>
+      </c>
+      <c r="H1078" t="inlineStr">
+        <is>
+          <t>added 2026-08-24: BTC-related sector grouping</t>
+        </is>
+      </c>
+      <c r="I1078" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" t="inlineStr">
+        <is>
+          <t>BITX</t>
+        </is>
+      </c>
+      <c r="B1079" t="inlineStr">
+        <is>
+          <t>2x Bitcoin Strategy ETF</t>
+        </is>
+      </c>
+      <c r="C1079" t="inlineStr">
+        <is>
+          <t>BTS</t>
+        </is>
+      </c>
+      <c r="D1079" t="inlineStr"/>
+      <c r="E1079" t="inlineStr"/>
+      <c r="F1079" t="n">
+        <v>852157760</v>
+      </c>
+      <c r="G1079" t="inlineStr">
+        <is>
+          <t>44 比特币概念</t>
+        </is>
+      </c>
+      <c r="H1079" t="inlineStr">
+        <is>
+          <t>added 2026-08-24: BTC-related sector grouping</t>
+        </is>
+      </c>
+      <c r="I1079" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" t="inlineStr">
+        <is>
+          <t>MARA</t>
+        </is>
+      </c>
+      <c r="B1080" t="inlineStr">
+        <is>
+          <t>MARA Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="C1080" t="inlineStr">
+        <is>
+          <t>NCM</t>
+        </is>
+      </c>
+      <c r="D1080" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="E1080" t="inlineStr">
+        <is>
+          <t>Capital Markets</t>
+        </is>
+      </c>
+      <c r="F1080" t="n">
+        <v>4318826496</v>
+      </c>
+      <c r="G1080" t="inlineStr">
+        <is>
+          <t>44 比特币概念</t>
+        </is>
+      </c>
+      <c r="H1080" t="inlineStr">
+        <is>
+          <t>added 2026-08-24: BTC-related sector grouping</t>
+        </is>
+      </c>
+      <c r="I1080" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" t="inlineStr">
+        <is>
+          <t>RIOT</t>
+        </is>
+      </c>
+      <c r="B1081" t="inlineStr">
+        <is>
+          <t>Riot Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="C1081" t="inlineStr">
+        <is>
+          <t>NCM</t>
+        </is>
+      </c>
+      <c r="D1081" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="E1081" t="inlineStr">
+        <is>
+          <t>Capital Markets</t>
+        </is>
+      </c>
+      <c r="F1081" t="n">
+        <v>7505178624</v>
+      </c>
+      <c r="G1081" t="inlineStr">
+        <is>
+          <t>44 比特币概念</t>
+        </is>
+      </c>
+      <c r="H1081" t="inlineStr">
+        <is>
+          <t>added 2026-08-24: BTC-related sector grouping</t>
+        </is>
+      </c>
+      <c r="I1081" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" t="inlineStr">
+        <is>
+          <t>CLSK</t>
+        </is>
+      </c>
+      <c r="B1082" t="inlineStr">
+        <is>
+          <t>CleanSpark, Inc.</t>
+        </is>
+      </c>
+      <c r="C1082" t="inlineStr">
+        <is>
+          <t>NCM</t>
+        </is>
+      </c>
+      <c r="D1082" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="E1082" t="inlineStr">
+        <is>
+          <t>Capital Markets</t>
+        </is>
+      </c>
+      <c r="F1082" t="n">
+        <v>3063827712</v>
+      </c>
+      <c r="G1082" t="inlineStr">
+        <is>
+          <t>44 比特币概念</t>
+        </is>
+      </c>
+      <c r="H1082" t="inlineStr">
+        <is>
+          <t>added 2026-08-24: BTC-related sector grouping</t>
+        </is>
+      </c>
+      <c r="I1082" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" t="inlineStr">
+        <is>
+          <t>CORZ</t>
+        </is>
+      </c>
+      <c r="B1083" t="inlineStr">
+        <is>
+          <t>Core Scientific, Inc.</t>
+        </is>
+      </c>
+      <c r="C1083" t="inlineStr">
+        <is>
+          <t>NMS</t>
+        </is>
+      </c>
+      <c r="D1083" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1083" t="inlineStr">
+        <is>
+          <t>Software - Infrastructure</t>
+        </is>
+      </c>
+      <c r="F1083" t="n">
+        <v>5549549568</v>
+      </c>
+      <c r="G1083" t="inlineStr">
+        <is>
+          <t>44 比特币概念</t>
+        </is>
+      </c>
+      <c r="H1083" t="inlineStr">
+        <is>
+          <t>added 2026-08-24: BTC-related sector grouping</t>
+        </is>
+      </c>
+      <c r="I1083" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" t="inlineStr">
+        <is>
+          <t>CIFR</t>
+        </is>
+      </c>
+      <c r="B1084" t="inlineStr">
+        <is>
+          <t>Cipher Digital Inc.</t>
+        </is>
+      </c>
+      <c r="C1084" t="inlineStr">
+        <is>
+          <t>NMS</t>
+        </is>
+      </c>
+      <c r="D1084" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E1084" t="inlineStr">
+        <is>
+          <t>Information Technology Services</t>
+        </is>
+      </c>
+      <c r="F1084" t="n">
+        <v>6374871552</v>
+      </c>
+      <c r="G1084" t="inlineStr">
+        <is>
+          <t>44 比特币概念</t>
+        </is>
+      </c>
+      <c r="H1084" t="inlineStr">
+        <is>
+          <t>added 2026-08-24: BTC-related sector grouping</t>
+        </is>
+      </c>
+      <c r="I1084" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" t="inlineStr">
+        <is>
+          <t>BTBT</t>
+        </is>
+      </c>
+      <c r="B1085" t="inlineStr">
+        <is>
+          <t>Bit Digital, Inc.</t>
+        </is>
+      </c>
+      <c r="C1085" t="inlineStr">
+        <is>
+          <t>NCM</t>
+        </is>
+      </c>
+      <c r="D1085" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="E1085" t="inlineStr">
+        <is>
+          <t>Capital Markets</t>
+        </is>
+      </c>
+      <c r="F1085" t="n">
+        <v>544556608</v>
+      </c>
+      <c r="G1085" t="inlineStr">
+        <is>
+          <t>44 比特币概念</t>
+        </is>
+      </c>
+      <c r="H1085" t="inlineStr">
+        <is>
+          <t>added 2026-08-24: BTC-related sector grouping</t>
+        </is>
+      </c>
+      <c r="I1085" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
